--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,12 +86,6 @@
     <t>cmd：命令字; 
 name：cl名字; 
 options: 选项(可选参数)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-insertor: 待插入数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -229,6 +223,34 @@
   </si>
   <si>
     <t xml:space="preserve">cmd：命令字; </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+insertor: 待插入数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+order: 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum：最大返回条数
+matcher：查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=query&amp;name=cs.cl&amp;order={"name":null}&amp;skip=0&amp;returnnum=2&amp;matcher={"name":\"hello\"}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -695,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="21.875" style="2" bestFit="1" customWidth="1"/>
@@ -742,16 +764,16 @@
     </row>
     <row r="3" spans="1:5" ht="24">
       <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -776,16 +798,16 @@
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -799,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
@@ -808,114 +830,124 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="36">
+    <row r="7" spans="1:5" ht="84">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48">
+    <row r="8" spans="1:5" ht="36">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="24">
+    <row r="9" spans="1:5" ht="48">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="36">
+    <row r="10" spans="1:5" ht="24">
       <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="36">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="72">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="72">
-      <c r="A11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3"/>
@@ -941,9 +973,16 @@
     <row r="17" spans="1:5">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -107,22 +107,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=update&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;selector={"name": \"hello\"}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd：命令字; 
-name：cl名字; 
-updator: 更新操作
-selector:更新条件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -251,6 +240,17 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=query&amp;name=cs.cl&amp;order={"name":null}&amp;skip=0&amp;returnnum=2&amp;matcher={"name":\"hello\"}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+updator: 更新操作
+matcher:更新条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=update&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;matcher={"name": \"hello\"}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -764,16 +764,16 @@
     </row>
     <row r="3" spans="1:5" ht="24">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -798,16 +798,16 @@
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
@@ -832,16 +832,16 @@
     </row>
     <row r="7" spans="1:5" ht="84">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>8</v>
@@ -866,16 +866,16 @@
     </row>
     <row r="9" spans="1:5" ht="48">
       <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>8</v>
@@ -883,16 +883,16 @@
     </row>
     <row r="10" spans="1:5" ht="24">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -900,53 +900,53 @@
     </row>
     <row r="11" spans="1:5" ht="36">
       <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72">
       <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -74,10 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=create collection&amp;name=cs.cl&amp;options={ShardingKey:{"age":1}}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cmd：命令字; 
 name：cs名字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -229,28 +225,32 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=create collection&amp;name=cs.cl&amp;options={ShardingKey:{"age":1}}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>cmd：命令字; 
 name：cl名字; 
-order: 排序字段名
+sort: 排序字段名
 selector: 查询结果列
 skip：跳过多少行
 returnnum：最大返回条数
-matcher：查询条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=query&amp;name=cs.cl&amp;order={"name":null}&amp;skip=0&amp;returnnum=2&amp;matcher={"name":\"hello\"}"</t>
+filter：查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=query&amp;name=cs.cl&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cmd：命令字; 
 name：cl名字; 
 updator: 更新操作
-matcher:更新条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=update&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;matcher={"name": \"hello\"}"</t>
+filter:更新条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=update&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;filter={"name": \"hello\"}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,7 +753,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -764,16 +764,16 @@
     </row>
     <row r="3" spans="1:5" ht="24">
       <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>8</v>
@@ -787,10 +787,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>8</v>
@@ -798,16 +798,16 @@
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>8</v>
@@ -821,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="7" spans="1:5" ht="84">
       <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -849,16 +849,16 @@
     </row>
     <row r="8" spans="1:5" ht="36">
       <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -866,10 +866,10 @@
     </row>
     <row r="9" spans="1:5" ht="48">
       <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>51</v>
@@ -883,16 +883,16 @@
     </row>
     <row r="10" spans="1:5" ht="24">
       <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>8</v>
@@ -900,53 +900,53 @@
     </row>
     <row r="11" spans="1:5" ht="36">
       <c r="A11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72">
       <c r="A12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -46,10 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=create collectionspace&amp;name=cs"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>coord/data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +104,6 @@
   </si>
   <si>
     <t>更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=drop collectionspace&amp;name=cs"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -251,6 +243,14 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=update&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;filter={"name": \"hello\"}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=create collectionspace&amp;name=cs"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=drop collectionspace&amp;name=cs"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,200 +753,200 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="24">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="36">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="36">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="84">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="36">
       <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48">
       <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="24">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="36">
       <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72">
       <c r="A12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=insert&amp;name=cs.cl&amp;insertor={"age":12, "name":\"hello\"}"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>插入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -251,6 +247,10 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=drop collectionspace&amp;name=cs"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=insert&amp;name=cs.cl&amp;insertor={"age":12, "name":\"hello\"}"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,10 +753,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -764,16 +764,16 @@
     </row>
     <row r="3" spans="1:5" ht="24">
       <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>7</v>
@@ -787,10 +787,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>7</v>
@@ -798,16 +798,16 @@
     </row>
     <row r="5" spans="1:5" ht="24">
       <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
@@ -815,16 +815,16 @@
     </row>
     <row r="6" spans="1:5" ht="36">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>7</v>
@@ -832,16 +832,16 @@
     </row>
     <row r="7" spans="1:5" ht="84">
       <c r="A7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
@@ -849,16 +849,16 @@
     </row>
     <row r="8" spans="1:5" ht="36">
       <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
@@ -866,16 +866,16 @@
     </row>
     <row r="9" spans="1:5" ht="48">
       <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
@@ -883,16 +883,16 @@
     </row>
     <row r="10" spans="1:5" ht="24">
       <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
@@ -900,53 +900,53 @@
     </row>
     <row r="11" spans="1:5" ht="36">
       <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="72">
       <c r="A12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -251,6 +251,42 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=insert&amp;name=cs.cl&amp;insertor={"age":12, "name":\"hello\"}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queryandupdate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>queryandremove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandremove&amp;name=cs.cl&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字;
+updator: 更新操作
+sort: 排序字段名
+selector: 查询结果列
+skip：跳过多少行
+returnnum：最大返回条数
+filter：查询条件
+returnnew:是否返回更新后记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;updator={"$inc":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"&amp;returnnew=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -361,74 +397,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -440,7 +408,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -717,12 +685,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="21.875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
@@ -847,121 +815,141 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="36">
+    <row r="8" spans="1:5" ht="108">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="48">
+    <row r="9" spans="1:5" ht="84">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="24">
+    <row r="10" spans="1:5" ht="36">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="36">
+    <row r="11" spans="1:5" ht="48">
       <c r="A11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="36">
+      <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="72">
-      <c r="A12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="3"/>
+    <row r="14" spans="1:5" ht="72">
+      <c r="A14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3"/>
@@ -980,9 +968,23 @@
     <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -276,7 +276,7 @@
   <si>
     <t>cmd：命令字; 
 name：cl名字;
-updator: 更新操作
+update: 更新操作
 sort: 排序字段名
 selector: 查询结果列
 skip：跳过多少行
@@ -286,7 +286,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;updator={"$inc":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"&amp;returnnew=true</t>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;update={"$inc":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"&amp;returnnew=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -276,7 +276,7 @@
   <si>
     <t>cmd：命令字; 
 name：cl名字;
-update: 更新操作
+updator: 更新操作
 sort: 排序字段名
 selector: 查询结果列
 skip：跳过多少行
@@ -286,7 +286,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;update={"$inc":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={"name":\"hello\"}"&amp;returnnew=true</t>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;updator={\"$inc\":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={\"name\":\"hello\"}"&amp;returnnew=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -287,6 +287,26 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=queryandupdate&amp;name=cs.cl&amp;updator={\"$inc\":{age:1}}&amp;sort={"name":null}&amp;skip=0&amp;returnnum=2&amp;filter={\"name\":\"hello\"}"&amp;returnnew=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新或插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+name：cl名字; 
+updator: 更新操作
+filter:更新条件
+setoninsert:插入数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=upsert&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;filter={"name": \"hello\"}"&amp;setoninsert={"sex":"male"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -685,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="21.875" style="2" bestFit="1" customWidth="1"/>
@@ -883,80 +903,90 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="24">
+    <row r="12" spans="1:5" ht="60">
       <c r="A12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24">
+      <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="36">
-      <c r="A13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="36">
+      <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="72">
-      <c r="A14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" ht="72">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3"/>
@@ -982,9 +1012,16 @@
     <row r="20" spans="1:5">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="127">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -307,6 +307,262 @@
   </si>
   <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=upsert&amp;name=cs.cl&amp;updator={\$set:{\"age\":100}}&amp;filter={"name": \"hello\"}"&amp;setoninsert={"sex":"male"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list contexts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list contexts current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list sessions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list sessions current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list storageunits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list domains</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list collectionspaces in domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list collections in domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list collections</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list collectionspaces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list lobs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上下文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前会话上下文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字; 
+sort: 排序字段名
+selector: 查询结果列
+filter：查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list contexts"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord/om</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前会话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储单元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后台任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域内cs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域内cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list contexts current"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list sessions"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list sessions current"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list storageunits"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list domains"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list collectionspaces in domain"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list collections in domain"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list tasks"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list collections"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list collectionspaces"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列出lob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd：命令字
+name：表名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">当前会话上下文 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">数据库 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">当前会话 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">集合空间 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">编目信息 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot contexts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot contexts"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=list lobs&amp;name=cs.cl"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot contexts current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot contexts current"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot database</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot database"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot sessions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot sessions"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot sessions current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot sessions current"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot system</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot system"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot collections</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot collections"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot collectionspaces</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot collectionspaces"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curl http://192.168.20.197:50004/  -d "cmd=snapshot catalog"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,9 +652,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -411,12 +664,83 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -428,7 +752,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -705,10 +1029,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="21.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="56.75" style="1" customWidth="1"/>
@@ -716,25 +1040,25 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -751,7 +1075,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="24">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -760,7 +1084,7 @@
       <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -768,7 +1092,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="36">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -785,7 +1109,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="24">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -802,7 +1126,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="36">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -819,7 +1143,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="84">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -836,7 +1160,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="108">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -853,7 +1177,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="84">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -870,7 +1194,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="36">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -887,7 +1211,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="48">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -904,7 +1228,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="60">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -921,7 +1245,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="24">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -938,7 +1262,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="36">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -955,7 +1279,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="72">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -972,7 +1296,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -988,40 +1312,425 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="3"/>
+    <row r="17" spans="1:5" ht="48">
+      <c r="A17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="48">
+      <c r="A18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="48">
+      <c r="A19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="48">
+      <c r="A20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="48">
+      <c r="A21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="48">
+      <c r="A22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="48">
+      <c r="A23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="48">
+      <c r="A24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="48">
+      <c r="A25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="48">
+      <c r="A26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="48">
+      <c r="A27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="24">
+      <c r="A28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="48">
+      <c r="A29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="48">
+      <c r="A30" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="48">
+      <c r="A31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="48">
+      <c r="A32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="48">
+      <c r="A33" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="48">
+      <c r="A34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="48">
+      <c r="A35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="48">
+      <c r="A36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="48">
+      <c r="A37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="4"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="4"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="4"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="4"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="4"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="4"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="4"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
+++ b/internal_doc/03.开发设计/rest/sequoiadb引擎rest接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="118">
   <si>
     <t>命令</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -326,19 +326,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>list storageunits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>list domains</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list collectionspaces in domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list collections in domain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -389,10 +377,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>存储单元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -409,14 +393,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>域内cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>域内cl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=list contexts current"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -429,19 +405,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=list storageunits"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>curl http://192.168.20.197:50004/  -d "cmd=list domains"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=list collectionspaces in domain"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>curl http://192.168.20.197:50004/  -d "cmd=list collections in domain"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1029,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="20.625" style="1" customWidth="1"/>
@@ -1317,16 +1281,16 @@
         <v>64</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="48">
@@ -1334,16 +1298,16 @@
         <v>65</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="48">
@@ -1351,16 +1315,16 @@
         <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="48">
@@ -1368,16 +1332,16 @@
         <v>67</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="48">
@@ -1385,16 +1349,16 @@
         <v>68</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="48">
@@ -1402,16 +1366,16 @@
         <v>69</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="48">
@@ -1419,16 +1383,16 @@
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="48">
@@ -1436,238 +1400,208 @@
         <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="48">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="24">
       <c r="A25" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="48">
       <c r="A26" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="48">
       <c r="A27" s="4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="24">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="48">
       <c r="A28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="D28" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="48">
       <c r="A29" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="48">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="48">
       <c r="A31" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="48">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>81</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="48">
       <c r="A33" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="48">
       <c r="A34" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="48">
-      <c r="A35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="48">
-      <c r="A36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="48">
-      <c r="A37" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="4"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="4"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="4"/>
@@ -1710,27 +1644,6 @@
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="4"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="4"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="4"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
